--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Event_Name</t>
   </si>
@@ -24,6 +24,75 @@
   </si>
   <si>
     <t>VO Automation Event 8014</t>
+  </si>
+  <si>
+    <t>VO Automation Event 25819</t>
+  </si>
+  <si>
+    <t>VO Automation Event 65944</t>
+  </si>
+  <si>
+    <t>VO Automation Event 37524</t>
+  </si>
+  <si>
+    <t>VO Automation Event 39634</t>
+  </si>
+  <si>
+    <t>VO Automation Event 94898</t>
+  </si>
+  <si>
+    <t>VO Automation Event 16314</t>
+  </si>
+  <si>
+    <t>VO Automation Event 77185</t>
+  </si>
+  <si>
+    <t>VO Automation Event 8407</t>
+  </si>
+  <si>
+    <t>VO Automation Event 81181</t>
+  </si>
+  <si>
+    <t>VO Automation Event 87501</t>
+  </si>
+  <si>
+    <t>VO Automation Event 65261</t>
+  </si>
+  <si>
+    <t>VO Automation Event 26221</t>
+  </si>
+  <si>
+    <t>VO Automation Event 31620</t>
+  </si>
+  <si>
+    <t>VO Automation Event 96970</t>
+  </si>
+  <si>
+    <t>VO Automation Event 51841</t>
+  </si>
+  <si>
+    <t>VO Automation Event 46986</t>
+  </si>
+  <si>
+    <t>VO Automation Event 27359</t>
+  </si>
+  <si>
+    <t>VO Automation Event 11962</t>
+  </si>
+  <si>
+    <t>VO Automation Event 41556</t>
+  </si>
+  <si>
+    <t>VO Automation Event 9135</t>
+  </si>
+  <si>
+    <t>VO Automation Event 9266</t>
+  </si>
+  <si>
+    <t>VO Automation Event 68870</t>
+  </si>
+  <si>
+    <t>VO Automation Event 58543</t>
   </si>
 </sst>
 </file>
@@ -68,7 +137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -91,6 +160,121 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Event_Name</t>
   </si>
@@ -93,6 +93,33 @@
   </si>
   <si>
     <t>VO Automation Event 58543</t>
+  </si>
+  <si>
+    <t>VO Automation Event 71814</t>
+  </si>
+  <si>
+    <t>Blood Donation Drive Kota</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Patna</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Lucknow</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Noida</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Gurugram</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Indore</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Bhopal</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Agra</t>
   </si>
 </sst>
 </file>
@@ -137,7 +164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -275,6 +302,51 @@
         <v>26</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
   <si>
     <t>Event_Name</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>Swachhta Hi Seva Prayagraj</t>
+  </si>
+  <si>
+    <t>Bhopal Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Ahmedabad Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Varanasi Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Prayagraj Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -191,7 +203,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -464,6 +476,31 @@
         <v>31</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
   <si>
     <t>Event_Name</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>Udaipur Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Faridabad Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -212,7 +215,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -535,6 +538,11 @@
         <v>51</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
   <si>
     <t>Event_Name</t>
   </si>
@@ -180,6 +180,9 @@
   </si>
   <si>
     <t>Nagpur Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Noida Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -224,7 +227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -572,6 +575,11 @@
         <v>55</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
